--- a/data/source/ed_assessment.xlsx
+++ b/data/source/ed_assessment.xlsx
@@ -327,7 +327,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Benzimidazole-2-thiol</t>
+          <t>2-phenoxyethanol</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -337,12 +337,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>209-502-6</t>
+          <t>204-589-7</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>583-39-1</t>
+          <t>122-99-6</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -374,7 +374,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Potassium dicyanoargentate</t>
+          <t>Benzimidazole-2-thiol</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>208-047-0</t>
+          <t>209-502-6</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>506-61-6</t>
+          <t>583-39-1</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -404,7 +404,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -421,7 +421,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Tris(2-ethylhexyl) phosphate</t>
+          <t>Potassium dicyanoargentate</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>201-116-6</t>
+          <t>208-047-0</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>78-42-2</t>
+          <t>506-61-6</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -468,37 +468,37 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>3-phenoxybenzyl-2-(4-ethoxyphenyl)-2-methylpropyl ether</t>
+          <t>Tris(2-ethylhexyl) phosphate</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>ETHOFENPROX; TREBON</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>407-980-2</t>
+          <t>201-116-6</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>80844-07-1</t>
+          <t>78-42-2</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Withdrawal of ED assessment</t>
+          <t>ED Expert Group meeting</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2025</t>
+          <t>18-Nov-2025</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -515,37 +515,37 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2-phenoxyethanol</t>
+          <t>3-phenoxybenzyl-2-(4-ethoxyphenyl)-2-methylpropyl ether</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ETHOFENPROX; TREBON</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>204-589-7</t>
+          <t>407-980-2</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>122-99-6</t>
+          <t>80844-07-1</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>ED Expert Group meeting</t>
+          <t>Withdrawal of ED assessment</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>23-Sep-2025</t>
+          <t>06-Oct-2025</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
